--- a/AI Audit Log_Đặng Nguyễn Anh Tài.xlsx
+++ b/AI Audit Log_Đặng Nguyễn Anh Tài.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FPT\Kì 7\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA39ECA-65B2-4DD6-B286-C7F1040842D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E14B07-2117-4048-A79B-75591581486E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="5" r:id="rId1"/>
     <sheet name="15-05-2026" sheetId="1" r:id="rId2"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId3"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId4"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId5"/>
+    <sheet name="20-05-2026" sheetId="6" r:id="rId3"/>
+    <sheet name="Assignment 1" sheetId="2" r:id="rId4"/>
+    <sheet name="Assignment 2" sheetId="3" r:id="rId5"/>
+    <sheet name="Assignment 3" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -222,13 +223,586 @@
   </si>
   <si>
     <t>Ai thực hiện</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>“Giải thích Use Case là gì, Actor là gì và khi nào cần dùng Use Case Diagram.”</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn tôi cách xác định Actor trong hệ thống bán hàng online.”</t>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn tôi cách xác định Use Case trong hệ thống thư viện.”</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“So sánh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>extend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong Use Case Diagram, cho ví dụ dễ hiểu.”</t>
+    </r>
+  </si>
+  <si>
+    <t>Process/Algorithm</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn từng bước cách vẽ Use Case Diagram đúng chuẩn UML cho hệ thống đặt đồ ăn.”</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn tôi viết Use Case Specification cho chức năng Đăng nhập.”</t>
+  </si>
+  <si>
+    <t>Reverse Engineering</t>
+  </si>
+  <si>
+    <t>“Tôi có source code Java Web MVC, hãy hướng dẫn cách phân tích code để tạo Use Case Diagram.”</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>“Hãy đóng vai giảng viên UML và đánh giá một Use Case Diagram tốt cần có tiêu chí nào.”</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>“Trong dự án thực tế, Use Case được BA, Developer và Tester sử dụng như thế nào?”</t>
+  </si>
+  <si>
+    <t>System Thinking</t>
+  </si>
+  <si>
+    <t>“Giải thích mối liên hệ từ Use Case đến Sequence Diagram, Class Diagram, Database Design và Code Implementation.”</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI &amp; Quyết định/Kiểm chứng của người học</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất các use case chính như Quản lý sách, Quản lý thành viên, Mượn sách, Trả sách, Gia hạn sách và Tìm kiếm sách. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi nhận thấy một số chức năng quá lớn nên cần tách nhỏ để dễ mô tả nghiệp vụ. Tôi quyết định phân rã các chức năng theo mục tiêu của người dùng thay vì theo từng nút bấm trên giao diện.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đưa ra quy trình gồm xác định phạm vi hệ thống, xác định actor, liệt kê use case, xác định quan hệ và sắp xếp bố cục diagram. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi ghi nhận rằng việc vẽ diagram cần đi theo thứ tự rõ ràng để tránh thiếu chức năng hoặc vẽ quá rối. Tôi quyết định dùng checklist này để kiểm tra lại diagram trước khi hoàn thiện.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI hướng dẫn xem Controller, Service, URL mapping và phân quyền người dùng để suy ra actor và use case. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi nhận thấy không nên chuyển từng hàm trong code thành use case vì sẽ làm diagram quá chi tiết. Tôi quyết định chỉ chọn những chức năng có ý nghĩa nghiệp vụ đối với người dùng.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là quan hệ dùng cho hành vi luôn xảy ra, còn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>extend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là hành vi mở rộng chỉ xảy ra trong một điều kiện nhất định. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi kiểm chứng bằng các ví dụ như đăng nhập, thanh toán và quên mật khẩu. Tôi quyết định dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho các bước bắt buộc và dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>extend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho các trường hợp phát sinh tùy điều kiện.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI cung cấp mẫu Use Case Specification gồm tên use case, actor, precondition, main flow, alternative flow, exception flow và postcondition. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi nhận thấy diagram chỉ mô tả tổng quan, còn specification giúp mô tả chi tiết luồng xử lý. Tôi quyết định viết thêm phần main flow và exception flow để tài liệu rõ ràng hơn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích BA dùng Use Case để mô tả yêu cầu, Developer dùng để hiểu luồng nghiệp vụ, còn Tester dùng để xây dựng test case. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi nhận ra Use Case không chỉ dùng để vẽ sơ đồ mà còn hỗ trợ giao tiếp giữa các vai trò trong dự án. Tôi quyết định xem Use Case như tài liệu nền tảng trước khi thiết kế và kiểm thử hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích Use Case mô tả yêu cầu nghiệp vụ, Sequence Diagram mô tả tương tác theo thời gian, Class Diagram mô tả cấu trúc đối tượng, Database Design lưu trữ dữ liệu và Code Implementation hiện thực hóa hệ thống.
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi ghi nhận rằng Use Case là bước đầu trong quá trình phân tích thiết kế hệ thống. Tôi quyết định học theo thứ tự Use Case → Sequence Diagram → Class Diagram → Database → Code để hiểu luồng phát triển phần mềm rõ hơn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI liệt kê các actor như Khách hàng, Admin, Shipper, Cổng thanh toán và Hệ thống email. AI cũng giải thích database không nên được xem là actor vì nó nằm bên trong hệ thống. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi kiểm chứng lại bằng nguyên tắc actor phải là đối tượng bên ngoài tương tác với hệ thống. Tôi quyết định chỉ giữ các actor thật sự có trao đổi thông tin với hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI định nghĩa Use Case là cách mô tả sự tương tác giữa người dùng hoặc hệ thống bên ngoài với hệ thống đang được phân tích. Actor là tác nhân thực hiện hoặc nhận kết quả từ hệ thống. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi ghi nhận rằng Use Case giúp tập trung vào chức năng nghiệp vụ thay vì giao diện. Tôi quyết định dùng Use Case Diagram để xác định phạm vi hệ thống trước khi đi vào thiết kế chi tiết.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đưa ra các tiêu chí như actor đúng, use case rõ nghĩa, boundary hợp lý, quan hệ include/extend không bị lạm dụng và diagram dễ đọc. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định/Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi dùng các tiêu chí này để rà soát lại sơ đồ của mình. Tôi quyết định chỉnh lại tên use case theo dạng động từ + đối tượng và loại bỏ các use case mang tính xử lý kỹ thuật nội bộ.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,6 +833,20 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -315,7 +903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -344,27 +932,38 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -701,7 +1300,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA04C5EC-7C86-4906-AABB-8FAEC13C660F}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.88671875" customWidth="1"/>
     <col min="2" max="2" width="26.77734375" customWidth="1"/>
@@ -710,7 +1309,7 @@
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -727,7 +1326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="57.6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -742,7 +1341,7 @@
       </c>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="57.6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -757,7 +1356,7 @@
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="57.6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -772,7 +1371,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="72">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -795,15 +1394,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.88671875" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" customWidth="1"/>
     <col min="3" max="3" width="24.21875" customWidth="1"/>
-    <col min="4" max="4" width="45" style="17" customWidth="1"/>
+    <col min="4" max="4" width="45" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="28.8">
       <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
@@ -813,12 +1412,12 @@
       <c r="C1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="172.8">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -828,11 +1427,11 @@
       <c r="C2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="172.8">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -842,11 +1441,11 @@
       <c r="C3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="172.8">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -856,15 +1455,15 @@
       <c r="C4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="16"/>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -872,27 +1471,199 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB988960-5E9B-43A8-A28C-2839992CFF24}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="22" style="18" customWidth="1"/>
+    <col min="3" max="3" width="45.77734375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="54.6640625" style="15" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="33.6" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="117.6" customHeight="1">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="108.6" customHeight="1">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="105" customHeight="1">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="123.6" customHeight="1">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="86.4">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="121.8" customHeight="1">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="99" customHeight="1">
+      <c r="A8" s="16">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="100.8">
+      <c r="A9" s="16">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="100.8">
+      <c r="A10" s="16">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="155.4" customHeight="1">
+      <c r="A11" s="16">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
